--- a/TestArticle.xlsx
+++ b/TestArticle.xlsx
@@ -2,31 +2,198 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Work projects\Web scraper\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Fitment data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="58">
   <si>
     <t>ArticleID</t>
+  </si>
+  <si>
+    <t>Model Dates:</t>
+  </si>
+  <si>
+    <t>Matching Models:</t>
+  </si>
+  <si>
+    <t>Model Options:</t>
+  </si>
+  <si>
+    <t>Links to diagrams:</t>
+  </si>
+  <si>
+    <t>09/2015-03/2018</t>
+  </si>
+  <si>
+    <t>AWS210-AEXLH</t>
+  </si>
+  <si>
+    <t>ROYAL, JPN, SED, 2ARFSE, D4, CVT, 4D</t>
+  </si>
+  <si>
+    <t>61-05 61-05</t>
+  </si>
+  <si>
+    <t>01/2013-08/2015</t>
+  </si>
+  <si>
+    <t>AWS210-AEXQH</t>
+  </si>
+  <si>
+    <t>ROY, JPN, SED, 2ARFSE, D4, CVT, 4D</t>
+  </si>
+  <si>
+    <t>AWS210-AEXUH</t>
+  </si>
+  <si>
+    <t>ROYG, JPN, SED, 2ARFSE, D4, CVT, 4D</t>
+  </si>
+  <si>
+    <t>AWS210-AEXWH</t>
+  </si>
+  <si>
+    <t>ATH, JPN, SED, 2ARFSE, D4, CVT, 4D</t>
+  </si>
+  <si>
+    <t>AWS210-AEXXH</t>
+  </si>
+  <si>
+    <t>ATHS, JPN, SED, 2ARFSE, D4, CVT, 4D</t>
+  </si>
+  <si>
+    <t>AWS210-AEXYH</t>
+  </si>
+  <si>
+    <t>ATHG, JPN, SED, 2ARFSE, D4, CVT, 4D</t>
+  </si>
+  <si>
+    <t>AWS211-AEXLH</t>
+  </si>
+  <si>
+    <t>07/2014-08/2015</t>
+  </si>
+  <si>
+    <t>AWS211-AEXQH</t>
+  </si>
+  <si>
+    <t>AWS211-AEXUH</t>
+  </si>
+  <si>
+    <t>AWS211-AEXWH</t>
+  </si>
+  <si>
+    <t>AWS211-AEXXH</t>
+  </si>
+  <si>
+    <t>AWS211-AEXYH</t>
+  </si>
+  <si>
+    <t>AWS215-AEXZH</t>
+  </si>
+  <si>
+    <t>MJ, JPN, SED, 2ARFSE, D4, CVT, 4D</t>
+  </si>
+  <si>
+    <t>GRS210-AETLH</t>
+  </si>
+  <si>
+    <t>ROYAL, JPN, SED, 4GRFSE, D4, ATM, 6FC, 4D</t>
+  </si>
+  <si>
+    <t>12/2012-08/2015</t>
+  </si>
+  <si>
+    <t>GRS210-AETQH</t>
+  </si>
+  <si>
+    <t>ROY, JPN, SED, 4GRFSE, D4, ATM, 6FC, 4D</t>
+  </si>
+  <si>
+    <t>GRS210-AETUH</t>
+  </si>
+  <si>
+    <t>ROYG, JPN, SED, 4GRFSE, D4, ATM, 6FC, 4D</t>
+  </si>
+  <si>
+    <t>GRS210-AETWH</t>
+  </si>
+  <si>
+    <t>ATH, JPN, SED, 4GRFSE, D4, ATM, 6FC, 4D</t>
+  </si>
+  <si>
+    <t>61-05</t>
+  </si>
+  <si>
+    <t>GRS210-AETXH</t>
+  </si>
+  <si>
+    <t>ATHS, JPN, SED, 4GRFSE, D4, ATM, 6FC, 4D</t>
+  </si>
+  <si>
+    <t>GRS210-AETYH</t>
+  </si>
+  <si>
+    <t>ATHG, JPN, SED, 4GRFSE, D4, ATM, 6FC, 4D</t>
+  </si>
+  <si>
+    <t>GRS211-AETLH</t>
+  </si>
+  <si>
+    <t>GRS211-AETQH</t>
+  </si>
+  <si>
+    <t>GRS211-AETUH</t>
+  </si>
+  <si>
+    <t>GRS211-AETWH</t>
+  </si>
+  <si>
+    <t>GRS211-AETXH</t>
+  </si>
+  <si>
+    <t>GRS211-AETYH</t>
+  </si>
+  <si>
+    <t>GRS214-AEZXH</t>
+  </si>
+  <si>
+    <t>ATHS, JPN, SED, 2GRFSE, D4, ATM, 8FC, 4D</t>
+  </si>
+  <si>
+    <t>GRS214-AEZYH</t>
+  </si>
+  <si>
+    <t>ATHG, JPN, SED, 2GRFSE, D4, ATM, 8FC, 4D</t>
+  </si>
+  <si>
+    <t>09/2013-08/2015</t>
+  </si>
+  <si>
+    <t>GWS214-AEXZB</t>
+  </si>
+  <si>
+    <t>MJ, JPN, SED, 2GRFXE, HTWC, CVT, 4D</t>
+  </si>
+  <si>
+    <t>81-11</t>
+  </si>
+  <si>
+    <t>81-11 81-11</t>
   </si>
 </sst>
 </file>
@@ -418,6 +585,1450 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D102"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>31</v>
+      </c>
+      <c r="B48" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" t="s">
+        <v>40</v>
+      </c>
+      <c r="D48" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" t="s">
+        <v>42</v>
+      </c>
+      <c r="D49" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>31</v>
+      </c>
+      <c r="B50" t="s">
+        <v>43</v>
+      </c>
+      <c r="C50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" t="s">
+        <v>44</v>
+      </c>
+      <c r="C51" t="s">
+        <v>33</v>
+      </c>
+      <c r="D51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" t="s">
+        <v>35</v>
+      </c>
+      <c r="D52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" t="s">
+        <v>47</v>
+      </c>
+      <c r="C54" t="s">
+        <v>40</v>
+      </c>
+      <c r="D54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" t="s">
+        <v>48</v>
+      </c>
+      <c r="C55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" t="s">
+        <v>49</v>
+      </c>
+      <c r="C56" t="s">
+        <v>50</v>
+      </c>
+      <c r="D56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" t="s">
+        <v>51</v>
+      </c>
+      <c r="C57" t="s">
+        <v>52</v>
+      </c>
+      <c r="D57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>53</v>
+      </c>
+      <c r="B58" t="s">
+        <v>54</v>
+      </c>
+      <c r="C58" t="s">
+        <v>55</v>
+      </c>
+      <c r="D58" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>5</v>
+      </c>
+      <c r="B65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>21</v>
+      </c>
+      <c r="B67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>21</v>
+      </c>
+      <c r="B68" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>5</v>
+      </c>
+      <c r="B70" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>5</v>
+      </c>
+      <c r="B72" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" t="s">
+        <v>30</v>
+      </c>
+      <c r="D73" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>31</v>
+      </c>
+      <c r="B74" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" t="s">
+        <v>33</v>
+      </c>
+      <c r="D74" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>31</v>
+      </c>
+      <c r="B75" t="s">
+        <v>34</v>
+      </c>
+      <c r="C75" t="s">
+        <v>35</v>
+      </c>
+      <c r="D75" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>31</v>
+      </c>
+      <c r="B76" t="s">
+        <v>36</v>
+      </c>
+      <c r="C76" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>31</v>
+      </c>
+      <c r="B77" t="s">
+        <v>39</v>
+      </c>
+      <c r="C77" t="s">
+        <v>40</v>
+      </c>
+      <c r="D77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>31</v>
+      </c>
+      <c r="B78" t="s">
+        <v>41</v>
+      </c>
+      <c r="C78" t="s">
+        <v>42</v>
+      </c>
+      <c r="D78" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>31</v>
+      </c>
+      <c r="B79" t="s">
+        <v>43</v>
+      </c>
+      <c r="C79" t="s">
+        <v>30</v>
+      </c>
+      <c r="D79" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>5</v>
+      </c>
+      <c r="B80" t="s">
+        <v>44</v>
+      </c>
+      <c r="C80" t="s">
+        <v>33</v>
+      </c>
+      <c r="D80" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>31</v>
+      </c>
+      <c r="B81" t="s">
+        <v>45</v>
+      </c>
+      <c r="C81" t="s">
+        <v>35</v>
+      </c>
+      <c r="D81" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>5</v>
+      </c>
+      <c r="B82" t="s">
+        <v>46</v>
+      </c>
+      <c r="C82" t="s">
+        <v>37</v>
+      </c>
+      <c r="D82" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>5</v>
+      </c>
+      <c r="B83" t="s">
+        <v>47</v>
+      </c>
+      <c r="C83" t="s">
+        <v>40</v>
+      </c>
+      <c r="D83" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>5</v>
+      </c>
+      <c r="B84" t="s">
+        <v>48</v>
+      </c>
+      <c r="C84" t="s">
+        <v>42</v>
+      </c>
+      <c r="D84" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>5</v>
+      </c>
+      <c r="B85" t="s">
+        <v>49</v>
+      </c>
+      <c r="C85" t="s">
+        <v>50</v>
+      </c>
+      <c r="D85" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>5</v>
+      </c>
+      <c r="B86" t="s">
+        <v>51</v>
+      </c>
+      <c r="C86" t="s">
+        <v>52</v>
+      </c>
+      <c r="D86" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>53</v>
+      </c>
+      <c r="B87" t="s">
+        <v>54</v>
+      </c>
+      <c r="C87" t="s">
+        <v>55</v>
+      </c>
+      <c r="D87" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>1</v>
+      </c>
+      <c r="B88" t="s">
+        <v>2</v>
+      </c>
+      <c r="C88" t="s">
+        <v>3</v>
+      </c>
+      <c r="D88" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>5</v>
+      </c>
+      <c r="B89" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>9</v>
+      </c>
+      <c r="B90" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>9</v>
+      </c>
+      <c r="B91" t="s">
+        <v>12</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>5</v>
+      </c>
+      <c r="B92" t="s">
+        <v>20</v>
+      </c>
+      <c r="C92" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>21</v>
+      </c>
+      <c r="B93" t="s">
+        <v>22</v>
+      </c>
+      <c r="C93" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>21</v>
+      </c>
+      <c r="B94" t="s">
+        <v>23</v>
+      </c>
+      <c r="C94" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95" t="s">
+        <v>27</v>
+      </c>
+      <c r="C95" t="s">
+        <v>28</v>
+      </c>
+      <c r="D95" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>5</v>
+      </c>
+      <c r="B96" t="s">
+        <v>29</v>
+      </c>
+      <c r="C96" t="s">
+        <v>30</v>
+      </c>
+      <c r="D96" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>31</v>
+      </c>
+      <c r="B97" t="s">
+        <v>32</v>
+      </c>
+      <c r="C97" t="s">
+        <v>33</v>
+      </c>
+      <c r="D97" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>31</v>
+      </c>
+      <c r="B98" t="s">
+        <v>34</v>
+      </c>
+      <c r="C98" t="s">
+        <v>35</v>
+      </c>
+      <c r="D98" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>31</v>
+      </c>
+      <c r="B99" t="s">
+        <v>43</v>
+      </c>
+      <c r="C99" t="s">
+        <v>30</v>
+      </c>
+      <c r="D99" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>5</v>
+      </c>
+      <c r="B100" t="s">
+        <v>44</v>
+      </c>
+      <c r="C100" t="s">
+        <v>33</v>
+      </c>
+      <c r="D100" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>31</v>
+      </c>
+      <c r="B101" t="s">
+        <v>45</v>
+      </c>
+      <c r="C101" t="s">
+        <v>35</v>
+      </c>
+      <c r="D101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>53</v>
+      </c>
+      <c r="B102" t="s">
+        <v>54</v>
+      </c>
+      <c r="C102" t="s">
+        <v>55</v>
+      </c>
+      <c r="D102" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>